--- a/Analysis/Prompt_Ablation/prompt_ablation_significance.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_significance.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,10 +502,10 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04480664780706643</v>
+        <v>0.06272930692989301</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7344186101356281</v>
+        <v>1</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -554,7 +554,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.238317757009363</v>
+        <v>12.81674208144804</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1551553072304037</v>
+        <v>0.00505014669881191</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -578,7 +578,7 @@
         <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9309318433824225</v>
+        <v>0.06565190708455483</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -592,7 +592,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.374269005847764</v>
+        <v>0.4588235294113474</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1463551373667468</v>
+        <v>0.9278399656641164</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -616,7 +616,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.9278399656641164</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -630,7 +630,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.25515463917518</v>
+        <v>5.238317757009363</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003896395492287</v>
+        <v>0.1551553072304037</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -654,10 +654,10 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0042860350415157</v>
+        <v>1</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -668,7 +668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.819469026548434</v>
+        <v>5.374269005847764</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1855039653793474</v>
+        <v>0.1463551373667468</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -692,7 +692,7 @@
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7420158615173894</v>
+        <v>1</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -701,12 +701,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -715,36 +715,36 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.512000000000226</v>
+        <v>18.25515463917518</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4695408390427462</v>
+        <v>0.0003896395492287</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>195</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4695408390427462</v>
+        <v>0.005844593238430501</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35.71096345514952</v>
+        <v>4.819469026548434</v>
       </c>
       <c r="E9" t="n">
-        <v>1.759797976492111e-08</v>
+        <v>0.1855039653793474</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>195</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.111757571790534e-07</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -782,7 +782,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.381868131868129</v>
+        <v>1.512000000000226</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1843472510611215</v>
+        <v>0.4695408390427462</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -806,7 +806,7 @@
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9217362553056075</v>
+        <v>0.9390816780854925</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.307116104868614</v>
+        <v>35.71096345514952</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1913677991860552</v>
+        <v>1.759797976492111e-08</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -844,10 +844,10 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5741033975581658</v>
+        <v>2.815676762387378e-07</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -858,7 +858,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.713168187744563</v>
+        <v>3.305623471882236</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05746471947316978</v>
+        <v>0.1915106734389272</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -882,7 +882,7 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4597177557853582</v>
+        <v>0.7660426937557088</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -896,7 +896,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.866873065015207</v>
+        <v>9.082644628098917</v>
       </c>
       <c r="E13" t="n">
-        <v>0.007201711790713942</v>
+        <v>0.01065930228527278</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -920,9 +920,161 @@
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06481540611642547</v>
+        <v>0.1172523251380006</v>
       </c>
       <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3.381868131868129</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1843472510611215</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>195</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.307116104868614</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1913677991860552</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>195</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9568389959302761</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.713168187744563</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.05746471947316978</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>195</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5746471947316978</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>top1</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9.866873065015207</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.007201711790713942</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>195</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0864205414885673</v>
+      </c>
+      <c r="J17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -937,7 +1089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,7 +1162,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1025,31 +1177,31 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7721.5</v>
+        <v>6323.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09531499286950784</v>
+        <v>6.27184108227982e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.05351742274819198</v>
+        <v>-0.1653122945430638</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>195</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5718899572170471</v>
+        <v>0.0003763104649367892</v>
       </c>
       <c r="L2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1060,7 +1212,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1075,17 +1227,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7750</v>
+        <v>7206</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1030686898467172</v>
+        <v>0.005557448978869397</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.05372781065088757</v>
+        <v>-0.09993425378040763</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1096,10 +1248,10 @@
         <v>195</v>
       </c>
       <c r="K3" t="n">
-        <v>0.515343449233586</v>
+        <v>0.02778724489434698</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1110,7 +1262,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1120,7 +1272,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>no_anchors</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1129,13 +1281,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8209.5</v>
+        <v>7676</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1714000665381105</v>
+        <v>0.06577301463894022</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04581196581196581</v>
+        <v>0.09556870479947403</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1146,7 +1298,7 @@
         <v>195</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6856002661524419</v>
+        <v>0.2630920585557609</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
@@ -1160,7 +1312,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1170,7 +1322,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1179,13 +1331,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8672</v>
+        <v>8075.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.375565758056344</v>
+        <v>0.09817429935809262</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03497698882314267</v>
+        <v>-0.1071137409598948</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1196,7 +1348,7 @@
         <v>195</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.2945228980742778</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -1210,7 +1362,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1220,7 +1372,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1229,13 +1381,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8909.5</v>
+        <v>8567</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5616222422686785</v>
+        <v>0.2105376083650431</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.009598948060486522</v>
+        <v>0.08499671268902038</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1246,7 +1398,7 @@
         <v>195</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.4210752167300862</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -1260,7 +1412,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1270,7 +1422,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>no_anchors</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1279,13 +1431,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7671</v>
+        <v>9352</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9655321439252218</v>
+        <v>0.7969783927609324</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009441157133464826</v>
+        <v>0.002998027613412229</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1296,7 +1448,7 @@
         <v>195</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9655321439252218</v>
+        <v>0.7969783927609324</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -1305,17 +1457,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1329,13 +1481,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6323.5</v>
+        <v>3120</v>
       </c>
       <c r="G8" t="n">
-        <v>6.27184108227982e-05</v>
+        <v>9.808888937121852e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1653122945430638</v>
+        <v>0.2761078238001315</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1346,7 +1498,7 @@
         <v>195</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003763104649367892</v>
+        <v>2.942666681136556e-07</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -1355,22 +1507,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1379,24 +1531,24 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7206</v>
+        <v>3238</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005557448978869397</v>
+        <v>0.0001119342467738097</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.09993425378040763</v>
+        <v>-0.1902432610124918</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>195</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02778724489434698</v>
+        <v>0.0002238684935476195</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -1405,22 +1557,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1429,13 +1581,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7676</v>
+        <v>2887</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06577301463894022</v>
+        <v>0.003070951076930591</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09556870479947403</v>
+        <v>0.1164234056541749</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1446,309 +1598,9 @@
         <v>195</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2630920585557609</v>
+        <v>0.003070951076930591</v>
       </c>
       <c r="L10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no_anchors</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>8075.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.09817429935809262</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.1071137409598948</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>195</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.2945228980742778</v>
-      </c>
-      <c r="L11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>cot_scaffold</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no_anchors</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>8567</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.2105376083650431</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.08499671268902038</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>195</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.4210752167300862</v>
-      </c>
-      <c r="L12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>no_anchors</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>scale_0_10</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>9352</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.7969783927609324</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.002998027613412229</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>195</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.7969783927609324</v>
-      </c>
-      <c r="L13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>top1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>cot_scaffold</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>3120</v>
-      </c>
-      <c r="G14" t="n">
-        <v>9.808888937121852e-08</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.2761078238001315</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>195</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.942666681136556e-07</v>
-      </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>top1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>cot_scaffold</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>scale_0_10</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>3238</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.0001119342467738097</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.1902432610124918</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>195</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.0002238684935476195</v>
-      </c>
-      <c r="L15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>top1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>scale_0_10</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>2887</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.003070951076930591</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.1164234056541749</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>195</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.003070951076930591</v>
-      </c>
-      <c r="L16" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1763,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1927,7 +1779,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1936,16 +1788,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05271646724718223</v>
+        <v>0.1881205303542168</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4416128900195241</v>
+        <v>0.6281499810440694</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3441025641025641</v>
+        <v>0.3521367521367522</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2667165562636561</v>
+        <v>0.4428246100533403</v>
       </c>
     </row>
     <row r="7">
@@ -1956,7 +1808,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1965,16 +1817,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.03925880845638263</v>
+        <v>0.2113384498493256</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4897657421622418</v>
+        <v>0.6604964952036377</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3271794871794872</v>
+        <v>0.3675213675213675</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3271711673924392</v>
+        <v>0.4425459495876129</v>
       </c>
     </row>
     <row r="8">
@@ -1985,7 +1837,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1994,16 +1846,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.09950595942880784</v>
+        <v>0.1262396069841691</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4417166005517963</v>
+        <v>0.6991261303585173</v>
       </c>
       <c r="F8" t="n">
-        <v>0.368091168091168</v>
+        <v>0.3606837606837607</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2906105571194027</v>
+        <v>0.4644813705392232</v>
       </c>
     </row>
     <row r="9">
@@ -2014,7 +1866,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2023,16 +1875,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9.022331875086142e-05</v>
+        <v>0.1775216582662204</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4561658327621874</v>
+        <v>0.6183939008834664</v>
       </c>
       <c r="F9" t="n">
-        <v>0.32</v>
+        <v>0.3504273504273504</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3135431044537824</v>
+        <v>0.4409502258232743</v>
       </c>
     </row>
     <row r="10">
@@ -2043,7 +1895,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2052,16 +1904,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05215995956934628</v>
+        <v>0.05271646724718223</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3422330610726274</v>
+        <v>0.4416128900195241</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2885470085470085</v>
+        <v>0.3441025641025641</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2487992231614218</v>
+        <v>0.2667165562636561</v>
       </c>
     </row>
     <row r="11">
@@ -2072,7 +1924,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2081,16 +1933,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.09595441595441596</v>
+        <v>0.03925880845638263</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5442791076118285</v>
+        <v>0.4897657421622418</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3357264957264957</v>
+        <v>0.3271794871794872</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3435004003475349</v>
+        <v>0.3271711673924392</v>
       </c>
     </row>
     <row r="12">
@@ -2101,7 +1953,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2110,16 +1962,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02447314788363281</v>
+        <v>0.09950595942880784</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3270952256837797</v>
+        <v>0.4417166005517963</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3712820512820513</v>
+        <v>0.368091168091168</v>
       </c>
       <c r="G12" t="n">
-        <v>0.239621474339932</v>
+        <v>0.2906105571194027</v>
       </c>
     </row>
     <row r="13">
@@ -2130,7 +1982,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2139,27 +1991,27 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01493740916077781</v>
+        <v>9.022331875086142e-05</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3877023542067298</v>
+        <v>0.4561658327621874</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3292307692307693</v>
+        <v>0.32</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2852326290181783</v>
+        <v>0.3135431044537824</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2168,27 +2020,27 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3043558774812271</v>
+        <v>-0.05215995956934628</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4948188696709069</v>
+        <v>0.3422330610726274</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5517948717948717</v>
+        <v>0.2885470085470085</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3654320405523109</v>
+        <v>0.2487992231614218</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2197,74 +2049,74 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1797599859730368</v>
+        <v>0.09595441595441596</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6444824218485817</v>
+        <v>0.5442791076118285</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.3357264957264957</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4111420687393655</v>
+        <v>0.3435004003475349</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>no_anchors</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2448104830132161</v>
+        <v>0.02447314788363281</v>
       </c>
       <c r="E16" t="n">
-        <v>0.492085643893181</v>
+        <v>0.3270952256837797</v>
       </c>
       <c r="F16" t="n">
-        <v>0.477948717948718</v>
+        <v>0.3712820512820513</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3564948163124203</v>
+        <v>0.239621474339932</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2619994766592648</v>
+        <v>0.01493740916077781</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4870339862480996</v>
+        <v>0.3877023542067298</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4543589743589743</v>
+        <v>0.3292307692307693</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3651281011740727</v>
+        <v>0.2852326290181783</v>
       </c>
     </row>
     <row r="18">
@@ -2275,25 +2127,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.2054972818323348</v>
+        <v>0.3043558774812271</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5427382828743136</v>
+        <v>0.4948188696709069</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4426495726495726</v>
+        <v>0.5517948717948717</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3643752043039668</v>
+        <v>0.3654320405523109</v>
       </c>
     </row>
     <row r="19">
@@ -2304,25 +2156,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.2610929704125467</v>
+        <v>0.1797599859730368</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4636756369809202</v>
+        <v>0.6444824218485817</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4892307692307692</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3523659693670232</v>
+        <v>0.4111420687393655</v>
       </c>
     </row>
     <row r="20">
@@ -2333,25 +2185,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.2051161113291622</v>
+        <v>0.2448104830132161</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3961856811802464</v>
+        <v>0.492085643893181</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4738461538461539</v>
+        <v>0.477948717948718</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3215347809874001</v>
+        <v>0.3564948163124203</v>
       </c>
     </row>
     <row r="21">
@@ -2362,25 +2214,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1957489388554643</v>
+        <v>0.3265215998205405</v>
       </c>
       <c r="E21" t="n">
-        <v>0.566195723044378</v>
+        <v>0.6507625572111446</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4000854700854701</v>
+        <v>0.4769230769230769</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3682895102131468</v>
+        <v>0.4712923572836843</v>
       </c>
     </row>
     <row r="22">
@@ -2391,24 +2243,227 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.2436026802521506</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.6352007482277204</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4094017094017094</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.4477862512418023</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.2511986164105514</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6576575097862515</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.4170940170940171</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.4644813705392233</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.2619994766592648</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4870339862480996</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.4543589743589743</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.3651281011740727</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.2054972818323348</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5427382828743136</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4426495726495726</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.3643752043039668</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.2610929704125467</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.4636756369809202</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4892307692307692</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.3523659693670232</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>qwen</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.2051161113291622</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.3961856811802464</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.4738461538461539</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.3215347809874001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.1957489388554643</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.566195723044378</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.4000854700854701</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.3682895102131468</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>scale_0_10</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D29" t="n">
         <v>0.1011253708109534</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E29" t="n">
         <v>0.3976688282669498</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F29" t="n">
         <v>0.4071794871794872</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G29" t="n">
         <v>0.2924298199176261</v>
       </c>
     </row>
